--- a/publications.xlsx
+++ b/publications.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,35 +425,40 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:E139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Faculty Name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Venue</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A Sharma</t>
+          <t>Abhishek Sharma</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -449,59 +466,74 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AI in Healthcare</t>
+          <t>Optimized MAC Protocol Using Fuzzy-Based Framework for Cognitive Radio AdHoc Networks.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>IEEE Journal</t>
+          <t>IEEE Access</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>DBLP</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A Sharma</t>
+          <t>Abhishek Sharma</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Machine Learning Model</t>
+          <t>On Optimizing Human-Machine Task Assignments.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Springer Conference</t>
+          <t>CoRR</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>DBLP</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A Sharma</t>
+          <t>Abhishek Sharma</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Deep Learning Study</t>
+          <t>Open X-Embodiment: Robotic Learning Datasets and RT-X Models : Open X-Embodiment Collaboration.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Elsevier Journal</t>
+          <t>ICRA</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>DBLP</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R Singh</t>
+          <t>Abhishek Singh Rathore</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -509,72 +541,3599 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Data Mining Techniques</t>
+          <t>Fast Similarity Search in Large-Scale Iris Databases Using High-Dimensional Hashing.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>IEEE Conference</t>
+          <t>BDA</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>DBLP</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R Singh</t>
+          <t>Abhishek Singh Rathore</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2022</v>
+        <v>2026</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Big Data Analysis</t>
+          <t>A secure framework for optimized data transmission using steganographic techniques.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Elsevier Journal</t>
+          <t>J. Big Data</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>DBLP</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Anjali Gupta</t>
+          <t>Abhishek Singh Rathore</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cloud Computing Research</t>
+          <t>Privacy preserving data analytics in DEI empowered IoV.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Springer Journal</t>
+          <t>Discov. Comput.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>DBLP</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Abhishek Tripathi</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>A CNN-SVM based computer aided diagnosis of breast Cancer using histogram K-means segmentation technique.</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Multim. Tools Appl.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Abhishek Tripathi</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>WeedGan: a novel generative adversarial network for cotton weed identification.</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Vis. Comput.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Abhishek Tripathi</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>A Systematic Survey on COVID 19 Detection and Diagnosis by Utilizing Deep Learning Techniques and Modalities of Radiology.</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>IC3</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Anand Prakash</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>A context-sensitive multi-tier deep learning framework for multimodal sentiment analysis.</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Multim. Tools Appl.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Anand Prakash</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>A machine learning-based approach to determine infection status in recipients of BBV152 (Covaxin) whole-virion inactivated SARS-CoV-2 vaccine for serological surveys.</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Comput. Biol. Medicine</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Anand Prakash</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Demo Abstract: Demonstration of Using Sensor Fusion for Constructing a Cost-Effective Smart-Door.</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>e-Energy</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Anand Rajavat</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Perceptual Operating Systems for the Trade Associations of Cyber Criminals to Scrutinize Hazardous Content.</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Int. J. Cyber Warf. Terror.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Anand Rajavat</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Illicit Events Evaluation Using NSGA-2 Algorithms Based on Energy Consumption.</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Informatica</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Anand Rajavat</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Pratiti ...Becoming Aware: Promoting Simulations and Games on a Global Platform.</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>ISAGA</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>Anjali Gupta</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>IoT Applications</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>IEEE Conference</t>
+      <c r="B17" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Understanding the Role of Time in Content Selection Decisions on OTT Platforms.</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TDIT</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Anjali Gupta</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Evaluating diversity and stereotypes amongst AI generated representations of healthcare providers.</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Frontiers Digit. Health</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Anjali Gupta</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>A Bipedal detection and tracking algorithm using 2D LiDAR.</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>ICCCNT</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Ankur Bhardwaj</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Enhanced Moth Flame Optimization Algorithm Entropy-Based Centroid SVM-Based Software Defect Prediction.</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>J. Electron. Test.</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Ankur Bhardwaj</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>A Hypergraph Approach to Deep Learning Based Routing in Software-Defined Vehicular Networks.</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>IEEE Trans. Mob. Comput.</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Ankur Bhardwaj</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Applying Machine Learning to Maximize Agricultural Yield to Handle the Food Crisis and Sustainable Growth.</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Int. J. Appl. Logist.</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Anuradha H Deshpande</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>2006</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Human protein reference database - 2006 update.</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Nucleic Acids Res.</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Anurag Joshi</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Grapho: Bringing line chart accessibility to the visually impaired.</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>IndiaHCI</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Anurag Joshi</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>A Two-Stage Fuzzy Multiobjective Optimization for Phase-Sensitive Day-Ahead Dispatch of Battery Energy Storage System.</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>IEEE Syst. J.</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Anurag Joshi</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>TicTorque: diagnosing effects of blink tics through mobile EEG headsets.</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>UbiComp/ISWC Adjunct</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Arindam Bose</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Leveraging Synthetic Adult Datasets for Unsupervised Infant Pose Estimation.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>CVPR Workshops</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Arindam Bose</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Unsupervised Domain Adaptation for Occlusion Resilient Human Pose Estimation.</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>CoRR</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Arindam Bose</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Uncertainty-Aware Diffusion Guided Refinement of 3D Scenes.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>CoRR</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Aslam</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Black Hole Attack Prevention in Mobile Ad-hoc Network (MANET) using Ant Colony Optimization Technique.</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Inf. Technol. Control.</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Aslam</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Real-Time Detection and Prevention of DoS Attack in Unmanned Marine Vehicles Using Machine Learning.</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Secur. Priv.</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Aslam</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>M2FMoE: Multi-Resolution Multi-View Frequency Mixture-of-Experts for Extreme-Adaptive Time Series Forecasting.</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>AAAI</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Asmita Sharma</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>InfVIKOR: A Decision-Making Computational Approach to Identify Influential Nodes in Complex Networks.</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>SN Comput. Sci.</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Asmita Sharma</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>An ensemble approach to forecast COVID-19 incidences using linear and non-linear statistical models.</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Int. J. Comput. Appl. Technol.</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Asmita Sharma</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Mobile-Ready Automated Triage of Diabetic Retinopathy Using Digital Fundus Images.</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>CoRR</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Aswathy Menon</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>An Intelligent System for Preventing Accidents Due to Driver Distractions.</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>ICMLDE</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Aswathy Menon</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Joint Channel Estimation and Symbol Detection in MIMO-OFDM Systems: A Deep Learning Approach using Bi-LSTM.</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>COMSNETS</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Aswathy Menon</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Document summarization using dictionary learning.</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>ICACCI</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Chhavi Tiwari</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ubiquitous Crowdsourcing Model for Location Recommender System.</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>J. Comput.</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Gaurav Shrivastava</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Video Prediction by Modeling Videos as Continuous Multi-Dimensional Processes.</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>CVPR</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Gaurav Shrivastava</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Video Decomposition Prior: Editing Videos Layer by Layer.</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>ICLR</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gaurav Shrivastava</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Continuous Video Process: Modeling Videos as Continuous Multi-Dimensional Processes for Video Prediction.</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>CoRR</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Gauri Chauhan</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>A Four-Phase Spatio-Temporal and Quantum-Enhanced Framework for Traffic Speed Forecasting With Calibrated Uncertainty.</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>IEEE Access</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Gauri Chauhan</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>A Deep Learning and Channel Sounding Based Data Authentication and QoS Enhancement Mechanism for Massive IoT Networks.</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Wirel. Pers. Commun.</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Jigyasu Dubey</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Pratiti ...Becoming Aware: Promoting Simulations and Games on a Global Platform.</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>ISAGA</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Jigyasu Dubey</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Gaming, Simulation and Innovations: Challenges and Opportunities - 52nd International Simulation and Gaming Association Conference, ISAGA 2021, Indore, India, September 6-10, 2021, Revised Selected Papers</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>['ISAGA', 'Lecture Notes in Computer Science']</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Jigyasu Dubey</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Development of the Player Satisfaction Scale - A Factor Analytic Study.</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>ISAGA</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Kamal Borana</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>TransEdgeNet: a self-supervised hybrid network with token pruning and temporal-spatial attention for real-time medical image segmentation.</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Biomed. Signal Process. Control.</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Manish Joshi</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>KBCNMUJAL@HASOC-Dravidian-CodeMix-FIRE2020: Using Machine Learning for Detection of Hate Speech and Offensive Code-Mixed Social Media text.</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>CoRR</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Manish Joshi</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>KBCNMUJAL@HASOC-Dravidian-CodeMix-FIRE2020: Using Machine Learning for Detection of Hate Speech and Offensive Codemix Social Media text.</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>FIRE</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Manish Joshi</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Distance and similarity measures of Hesitant bi-fuzzy set and its applications in renewable energy systems.</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Math. Comput. Simul.</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Naresh Purohit</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Channel Estimation for Sparse mm-Wave MIMO System.</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Wirel. Pers. Commun.</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Naresh Purohit</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Performance analysis of non-orthogonal multiple access in 5G mm-wave wireless networks.</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Int. J. Wirel. Mob. Comput.</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Naresh Purohit</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Spatially-Adaptive Image Restoration using Distortion-Guided Networks.</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>ICCV</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Neeraj Sahu</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Understanding Sidecars in Cloud Orchestration.</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>SESAME@EuroSys</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Neeraj Sahu</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>SoK: A Systems Perspective on Compound AI Threats and Countermeasures.</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>CoRR</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Neeraj Sahu</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Sidecars on the Central Lane: Impact of Network Proxies on Microservices.</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>CoRR</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Nikhil Chaturvedi</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>NTIRE 2025 Image Shadow Removal Challenge Report.</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>CVPR Workshops</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Nikhil Chaturvedi</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>NTIRE 2025 Image Shadow Removal Challenge Report.</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>CoRR</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Nikhil Chaturvedi</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Assessing micro-mobility services in pandemics for studying the 10-minutes cities concept in India using geospatial data analysis: an application.</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>IWCTS@SIGSPATIAL</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Nikita Dubey</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Vector-Valued Fuzzy Metric Spaces and Fixed Point Theorems.</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Axioms</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Nikita Dubey</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Coincidence Point of Edelstein Type Mappings in Fuzzy Metric Spaces and Application to the Stability of Dynamic Markets.</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Axioms</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Nikita Dubey</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Khalouta transform and applications to Caputo-fractional differential equations.</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Frontiers Appl. Math. Stat.</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Nilesh Patidar</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>An ultra-dense and cost-efficient coplanar RAM cell design in quantum-dot cellular automata technology.</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>J. Supercomput.</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Nilesh Patidar</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>An extensible architecture of 32-bit ALU for high-speed computing in QCA technology.</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>J. Supercomput.</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Nilesh Patidar</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Design and Analysis of Water Distribution Network Using Epanet 2.0 and Loop 4.0 - A Case Study of Narangi Village.</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>ICO</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Pavan K Gupta</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Efficient Collective Operations Using Remote Memory Operations on VIA-Based Clusters.</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>IPDPS</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Pavan K Gupta</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>The Perceptual Observatory Characterizing Robustness and Grounding in MLLMs.</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>CoRR</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Pavan K Gupta</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Compressive Light Field Reconstructions using Deep Learning.</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>CoRR</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Pawan Deep Shukla</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>A survey on digital image forensic methods based on blind forgery detection.</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Multim. Tools Appl.</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Poonam Yadav</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Optimization of fractional-order EPQ models with memory-dependent demand and shortage dynamics.</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Oper. Res.</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Poonam Yadav</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Sensor Injection Based Routing Protocol for Effective Load Balancing in Underwater Wireless Sensor Networks.</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Wirel. Pers. Commun.</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Poonam Yadav</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Energy Efficient Data Transmission in Wireless Body Area Network (WBAN).</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>SOFA</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Priyanka Chand</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>A Review of Machine Learning for Healthcare Informatics Specifically Tuberculosis Disease Diagnostics.</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>INTAP</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Priyanka Chand</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>refMLST: reference-based multilocus sequence typing enables universal bacterial typing.</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>BMC Bioinform.</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Priyanka Chand</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Machine learning based tuberculosis (ML-TB) health predictor model: early TB health disease prediction with ML models for prevention in developing countries.</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>PeerJ Comput. Sci.</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Rachana Jain</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Geometric-Stochastic Multimodal Deep Learning for Predictive Modeling of SUDEP and Stroke Vulnerability.</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>CoRR</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Rachana Jain</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Harnessing machine learning models for non-invasive pre-diabetes screening in children and adolescents.</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Comput. Methods Programs Biomed.</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Rashmi Sharma</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>A machine learning-based approach to determine infection status in recipients of BBV152 (Covaxin) whole-virion inactivated SARS-CoV-2 vaccine for serological surveys.</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Comput. Biol. Medicine</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Rashmi Sharma</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Reconstruction of Sea Surface Salinity Fields Over the Bay of Bengal Using Machine Learning Approach.</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>IEEE Trans. Geosci. Remote. Sens.</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Rashmi Sharma</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Digital Health Innovation: Exploring Adoption of COVID-19 Digital Contact Tracing Apps.</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>IEEE Trans. Engineering Management</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Reena Gupta</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>SiTe CiM: Signed Ternary Computing-in-Memory for Ultra-Low Precision Deep Neural Networks.</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>CoRR</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Reena Gupta</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Energy Efficient Cache Design with Piezoelectric FETs.</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>ISLPED</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Reena Gupta</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>STeP-CiM: Strain-enabled Ternary Precision Computation-in-Memory based on Non-Volatile 2D Piezoelectric Transistors.</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>CoRR</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Sandeep Kumar Jain</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>An Improved Particle Swarm Approach for Energy-Aware Location-Aided Routing in Mobile Ad-Hoc Network.</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>IC3I</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Sandeep Kumar Jain</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Spider Monkey Crow Optimization Algorithm With Deep Learning for Sentiment Classification and Information Retrieval.</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>IEEE Access</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Sandeep Kumar Jain</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>A journey of terahertz communication: An IRS integration perspective.</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Phys. Commun.</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Santosh Patel</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Manoeuvring of underwater snake robot with tail thrust using the actor-critic neural network super-twisting sliding mode control in the uncertain environment and disturbances.</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Neural Comput. Appl.</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Santosh Patel</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>3D dynamics and control of a snake robot in uncertain underwater environment.</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Robotica</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Santosh Patel</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Emulating Underwater Locomotion: Design and Development of CPG-Controlled Biomimetic Robotic Fish.</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>CoDIT</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Satish Kumar Patel</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Automated Flexible Needle Trajectory Planning for Keyhole Neurosurgery Using Reinforcement Learning.</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>IROS</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Satish Kumar Patel</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Mutation Effects on 3D-Structural Reorganization Using HIV-1 Protease as a Case Study.</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Encyclopedia of Bioinformatics and Computational Biology</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Satish Shukla</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Coincidence Point of Edelstein Type Mappings in Fuzzy Metric Spaces and Application to the Stability of Dynamic Markets.</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Axioms</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Satish Shukla</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>On Graphical Symmetric Spaces, Fixed-Point Theorems and the Existence of Positive Solution of Fractional Periodic Boundary Value Problems.</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Symmetry</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Satish Shukla</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Some Fixed Point Theorems for α-Admissible Mappings in Complex-Valued Fuzzy Metric Spaces.</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Symmetry</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Saurabh Jain</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Deep Learning-Assisted Urea Detection for Water Quality Monitoring: An Optimization Perspective.</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>J. Wirel. Mob. Networks Ubiquitous Comput. Dependable Appl.</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Saurabh Jain</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>A construction of post quantum secure authenticated key agreement design for mobile digital rights management system.</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Multim. Tools Appl.</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Saurabh Jain</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Eight pruning deep learning models for low storage and high-speed COVID-19 computed tomography lung segmentation and heatmap-based lesion localization: A multicenter study using COVLIAS 2.0.</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Comput. Biol. Medicine</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Shivang Dwivedi</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Adaptive Training on Basic AR Interactions: Bi-Variate Metrics and Neuroergonomic Evaluation Paradigms.</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Int. J. Hum. Comput. Interact.</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Shivang Dwivedi</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Impact of uses of Artificial Intelligence (AI) in Textile Industry in India.</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>ICCCNT</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Shivang Dwivedi</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>3D CNN with Localized Residual Connections for Hyperspectral Image Classification.</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>CVIP</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Shobha Jain</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Error and uncertainty estimation in gain measurement of double ridge horn antenna working for 1-18 GHz.</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Int. J. Syst. Assur. Eng. Manag.</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Shobha Jain</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Semicompatibility and fixed point theorems in an unbounded D-metric space.</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Int. J. Math. Math. Sci.</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Shobha Jain</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>The Impacts of Groundwater Recharge Rate Reduction on Agricultural Productivity in Nashik.</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>SN Comput. Sci.</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Shweta Agrawal</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Empirical Analysis of Phonological and Prosodic Features of Native and Non-Native Hindi Speakers.</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>O-COCOSDA</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Shweta Agrawal</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Study of Speech Recognition System Based on Transformer and Connectionist Temporal Classification Models for Low Resource Language.</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>SPECOM</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Shweta Agrawal</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>An Empirical Study of Speaker Identification System for Mono and Traverse Linguistic Background Using EM and SMEM.</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>O-COCOSDA</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Shweta Mishra</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>The Intersection of Computer Engineering and Intellectual Property Law.</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>ICCCNT</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Shweta Mishra</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Epistemic trust in generative AI for higher education scale (ETGAI-HE scale).</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>AI Soc.</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Shweta Mishra</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Integration of digital technologies in manufacturing: a survey of industry 4.0 applications and challenges.</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>J. Ambient Intell. Humaniz. Comput.</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Shyam Sundar Meena</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Revolutionizing Mobile Banking System: Novel ML-Based Approach for Securing Cloud Data.</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>J. Internet Serv. Inf. Secur.</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Shyam Sundar Meena</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Community detection in social networks by incorporating the preferential selection.</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>J. Complex Networks</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Shyam Sundar Meena</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>An Interactive Mobile Application for the Visually Impaired to Have Access to Listening Audio Books with Handy Books Portal.</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Int. J. Interact. Mob. Technol.</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Sonika Shrivastava</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Data encoding and cost optimised distribution for efficient and secure storage in cloud federation.</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Int. J. Inf. Comput. Secur.</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Supriya Vyas</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Industry 5.0 in Smart Education: Concepts, Applications, Challenges, Opportunities, and Future Directions.</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>IEEE Access</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Supriya Vyas</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Towards Smart Education in the Industry 5.0 Era: A Mini Review on the Application of Federated Learning.</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>DASC/PiCom/CBDCom/CyberSciTech</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Supriya Vyas</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>A Deep Learning Approach for Motion Segmentation Using An Optical Flow Technique.</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>ICCCNT</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Swati Dubey Mishra</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Surface grafted core-shell chitosan-modified solid lipid nanoparticles: characterization and application in hydrophobic drug delivery.</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>NEMS</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Swati Dubey Mishra</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>A mathematical model for red cell motion in narrow capillary surrounded by tissue.</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Appl. Math. Comput.</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Swati Sharma</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Task-Lens: Cross-Task Utility Based Speech Dataset Profiling for Low-Resource Indian Languages.</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>CoRR</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Swati Sharma</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Deep Reader: Information Extraction from Document Images via Relation Extraction and Natural Language.</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>ACCV Workshops</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Swati Sharma</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Automatic Classification of Low-Resolution Chromosomal Images.</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>ECCV Workshops</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Tanmay Kasbe</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>FRBF: A Fuzzy Rule Based Framework for Heart Disease Diagnosis.</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Inteligencia Artif.</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Tanmay Kasbe</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>A review on specification evaluation of broadcasting routing protocols in VANET.</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Comput. Sci. Rev.</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Tanmay Kasbe</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>A Survey on Chronic Kidney Disease Diagnosis Using Fuzzy Logic.</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>iSES</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Varsha Upadhyay</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Integrating Extractive Techniques and Classification Methods for Legal Document Summarization.</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Int. J. Data Warehous. Min.</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Varsha Upadhyay</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>A systematic data-driven approach for targeted marketing in enterprise information system.</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Enterp. Inf. Syst.</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Varsha Upadhyay</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Mitigating Risks in the Cloud-Based Metaverse Access Control Strategies and Techniques.</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Int. J. Cloud Appl. Comput.</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Vimal Kumar Dixit</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Analysing the empirical research in digital supply chain: a state of art literature review and future research directions.</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Oper. Res.</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Vimal Kumar Dixit</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Mobile Smart Contracts: Exploring Scalability Challenges and Consensus Mechanisms.</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>IEEE Access</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Vimal Kumar Dixit</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Legally Enforceable Smart-Contract Languages: A Systematic Literature Review.</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>ACM Comput. Surv.</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Yogita Agrawal</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>A machine learning-based approach to determine infection status in recipients of BBV152 (Covaxin) whole-virion inactivated SARS-CoV-2 vaccine for serological surveys.</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Comput. Biol. Medicine</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Yogita Agrawal</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Hierarchical clustering for multiple nominal data streams with evolving behaviour.</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Complex Intell. Syst.</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Anju Verma</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Multiple Image Watermarking for Efficient Storage and Transmission of Medical Images.</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>ICACDS</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Anju Verma</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>FEAST: Fog enabled auto-scaling technique for IoT-based cloud application.</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Clust. Comput.</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Anju Verma</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>ETSA-LP: Ensemble Time-Series Approach for Load Prediction in Cloud.</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Comput. Informatics</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Pooja Verma</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Improved adaptive type-2 fuzzy filter with exclusively two fuzzy membership function for filtering salt and pepper noise.</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Multim. Tools Appl.</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Pooja Verma</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Construction of Data Driven Decomposition Based Soft Sensors with Auto Encoder Deep Neural Network for IoT Healthcare Applications.</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Int. J. Commun. Networks Inf. Secur.</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>DBLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Pooja Verma</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Multivariable Event-Triggered Generalized Super-Twisting Controller for Safe Navigation of Nonholonomic Mobile Robot.</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>IEEE Syst. J.</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>DBLP</t>
         </is>
       </c>
     </row>
